--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908C4127-C248-4318-8EA6-928D84CFC88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C0D5B2B04FAA2875C674853670D85CA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2AF7C7F-46AC-4F61-AD4A-89EC708AD26D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 09-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 14-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C0D5B2B04FAA2875C674853670D85CA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2AF7C7F-46AC-4F61-AD4A-89EC708AD26D}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C0D534900FA93975C674853670D85CA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E296CC7E-660E-418A-A2B9-6D4B76AC716B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C0D534900FA93975C674853670D85CA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E296CC7E-660E-418A-A2B9-6D4B76AC716B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66172773-5857-42DE-8D54-9D95FEFF35BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66172773-5857-42DE-8D54-9D95FEFF35BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DE79D0-A766-468B-86D1-40F968649D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 14-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 17-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -55,7 +55,7 @@
     <t>WinPLC _Privath__ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _Privath__ (Xmedicus Systems)</t>
+    <t>Xmedicus _Privath__ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _Privath__ (CGM)</t>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DE79D0-A766-468B-86D1-40F968649D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AA8531-A5D1-4D60-95B0-0CEAACF57C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AA8531-A5D1-4D60-95B0-0CEAACF57C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9FA65FFABD98B2A75C674853670D85CA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E2BC348-1C7C-474B-BA6A-82D27FBFEF96}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 17-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 18-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9FA65FFABD98B2A75C674853670D85CA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E2BC348-1C7C-474B-BA6A-82D27FBFEF96}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9FAF5FCB9AD6B2375C674853670D85CA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DCA1045-A957-48A5-9E73-8EBC8443B749}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 18-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 21-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9FAF5FCB9AD6B2375C674853670D85CA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DCA1045-A957-48A5-9E73-8EBC8443B749}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A9559D-720B-41CF-A530-EEE1871E0140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1303,13 +1303,13 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A9559D-720B-41CF-A530-EEE1871E0140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BD9E9F-3D72-4294-9332-83DBA445F93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 21-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 22-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BD9E9F-3D72-4294-9332-83DBA445F93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A1ADEA-25DE-4251-A0C5-6A654028371B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A1ADEA-25DE-4251-A0C5-6A654028371B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9821B68-1933-4280-B8D0-8CA953E22DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 22-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 23-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9821B68-1933-4280-B8D0-8CA953E22DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB92CADBF9955EA2B75C674853670D85CAC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2E092BA-35B0-4674-877A-AB2521A09AA6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1268,13 +1268,13 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB92CADBF9955EA2B75C674853670D85CAC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2E092BA-35B0-4674-877A-AB2521A09AA6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{D4058E4F-D4F9-4DD1-B3C9-034D39C815D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 23-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 24-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -55,13 +55,13 @@
     <t>WinPLC _Privath__ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _Privath__ (XMedicus Systems)</t>
+    <t>XMedicus _Privath__ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _Privath__ (CGM)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0130X)</t>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="6_{D4058E4F-D4F9-4DD1-B3C9-034D39C815D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9EEADB2E36FCB2C75C674853670D85CAC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD013E33-A5B4-4D7E-B6F3-CF4229D0D0C2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9EEADB2E36FCB2C75C674853670D85CAC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD013E33-A5B4-4D7E-B6F3-CF4229D0D0C2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4602CB-AA62-4681-A8D2-1C304B3A44FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 24-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 28-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4602CB-AA62-4681-A8D2-1C304B3A44FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9B0D537D149892B7B36B38FCE70D85E9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E0013FA-7CB5-432C-BC83-206EAAE9DF0D}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 28-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 02-10-2026'!$A$1:$L$54</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="112">
   <si>
     <t>Standard</t>
   </si>
@@ -104,6 +104,12 @@
   </si>
   <si>
     <t>DDB (1.1)</t>
+  </si>
+  <si>
+    <t>Den Gode Blanketservice</t>
+  </si>
+  <si>
+    <t>DGB (0.91)</t>
   </si>
   <si>
     <t>Udskrivningsepikrise</t>
@@ -694,10 +700,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +741,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +884,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -926,11 +932,14 @@
       <c r="C7" t="s">
         <v>14</v>
       </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
       <c r="K7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -940,69 +949,45 @@
       <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>30</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1013,11 +998,14 @@
       <c r="D10" t="s">
         <v>15</v>
       </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
       <c r="F10" t="s">
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -1028,51 +1016,48 @@
       <c r="J10" t="s">
         <v>15</v>
       </c>
+      <c r="K10" t="s">
+        <v>18</v>
+      </c>
       <c r="L10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>33</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -1083,8 +1068,14 @@
       <c r="D12" t="s">
         <v>15</v>
       </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -1095,48 +1086,45 @@
       <c r="J12" t="s">
         <v>15</v>
       </c>
+      <c r="K12" t="s">
+        <v>16</v>
+      </c>
       <c r="L12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>36</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
@@ -1150,11 +1138,8 @@
       <c r="E14" t="s">
         <v>16</v>
       </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -1166,13 +1151,13 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1185,6 +1170,12 @@
       <c r="D15" t="s">
         <v>15</v>
       </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
@@ -1198,13 +1189,13 @@
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1217,9 +1208,6 @@
       <c r="D16" t="s">
         <v>15</v>
       </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
       <c r="G16" t="s">
         <v>15</v>
       </c>
@@ -1239,12 +1227,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -1256,7 +1244,7 @@
         <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -1268,15 +1256,15 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
         <v>44</v>
@@ -1288,10 +1276,10 @@
         <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -1309,7 +1297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1322,9 +1310,6 @@
       <c r="D19" t="s">
         <v>15</v>
       </c>
-      <c r="E19" t="s">
-        <v>16</v>
-      </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
@@ -1347,7 +1332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1360,11 +1345,14 @@
       <c r="D20" t="s">
         <v>15</v>
       </c>
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -1382,7 +1370,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1392,11 +1380,32 @@
       <c r="C21" t="s">
         <v>14</v>
       </c>
-      <c r="E21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1406,35 +1415,11 @@
       <c r="C22" t="s">
         <v>14</v>
       </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
       <c r="E22" t="s">
         <v>16</v>
       </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1447,6 +1432,9 @@
       <c r="D23" t="s">
         <v>15</v>
       </c>
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
       <c r="F23" t="s">
         <v>15</v>
       </c>
@@ -1469,7 +1457,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1479,11 +1467,32 @@
       <c r="C24" t="s">
         <v>14</v>
       </c>
-      <c r="E24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1493,66 +1502,45 @@
       <c r="C25" t="s">
         <v>14</v>
       </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>15</v>
+      </c>
+      <c r="L26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>59</v>
-      </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" t="s">
-        <v>15</v>
-      </c>
-      <c r="K26" t="s">
-        <v>15</v>
-      </c>
-      <c r="L26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>60</v>
       </c>
       <c r="B27" t="s">
         <v>61</v>
@@ -1563,11 +1551,14 @@
       <c r="D27" t="s">
         <v>15</v>
       </c>
+      <c r="E27" t="s">
+        <v>16</v>
+      </c>
       <c r="F27" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -1578,48 +1569,48 @@
       <c r="J27" t="s">
         <v>15</v>
       </c>
+      <c r="K27" t="s">
+        <v>15</v>
+      </c>
       <c r="L27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" t="s">
+        <v>15</v>
+      </c>
+      <c r="L28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>62</v>
-      </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" t="s">
-        <v>15</v>
-      </c>
-      <c r="K28" t="s">
-        <v>16</v>
-      </c>
-      <c r="L28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>63</v>
       </c>
       <c r="B29" t="s">
         <v>64</v>
@@ -1631,10 +1622,10 @@
         <v>15</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -1645,48 +1636,48 @@
       <c r="J29" t="s">
         <v>15</v>
       </c>
+      <c r="K29" t="s">
+        <v>16</v>
+      </c>
       <c r="L29" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>65</v>
-      </c>
-      <c r="C30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" t="s">
-        <v>18</v>
-      </c>
-      <c r="G30" t="s">
-        <v>18</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" t="s">
-        <v>15</v>
-      </c>
-      <c r="K30" t="s">
-        <v>15</v>
-      </c>
-      <c r="L30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>66</v>
       </c>
       <c r="B31" t="s">
         <v>67</v>
@@ -1698,10 +1689,10 @@
         <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -1712,48 +1703,48 @@
       <c r="J31" t="s">
         <v>15</v>
       </c>
+      <c r="K31" t="s">
+        <v>15</v>
+      </c>
       <c r="L31" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>68</v>
-      </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
-      <c r="K32" t="s">
-        <v>15</v>
-      </c>
-      <c r="L32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>69</v>
       </c>
       <c r="B33" t="s">
         <v>70</v>
@@ -1761,11 +1752,32 @@
       <c r="C33" t="s">
         <v>14</v>
       </c>
-      <c r="E33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" t="s">
+        <v>15</v>
+      </c>
+      <c r="K33" t="s">
+        <v>15</v>
+      </c>
+      <c r="L33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1834,11 +1846,8 @@
       <c r="E38" t="s">
         <v>16</v>
       </c>
-      <c r="K38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1885,8 +1894,11 @@
       <c r="E41" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1896,11 +1908,11 @@
       <c r="C42" t="s">
         <v>14</v>
       </c>
-      <c r="K42" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,23 +1926,23 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>91</v>
-      </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="K44" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>92</v>
       </c>
       <c r="B45" t="s">
         <v>93</v>
@@ -1938,14 +1950,11 @@
       <c r="C45" t="s">
         <v>14</v>
       </c>
-      <c r="F45" t="s">
-        <v>15</v>
-      </c>
       <c r="K45" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1955,14 +1964,14 @@
       <c r="C46" t="s">
         <v>14</v>
       </c>
-      <c r="E46" t="s">
-        <v>16</v>
-      </c>
       <c r="F46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1975,8 +1984,11 @@
       <c r="E47" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1989,14 +2001,8 @@
       <c r="E48" t="s">
         <v>16</v>
       </c>
-      <c r="F48" t="s">
-        <v>15</v>
-      </c>
-      <c r="K48" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2006,6 +2012,9 @@
       <c r="C49" t="s">
         <v>14</v>
       </c>
+      <c r="E49" t="s">
+        <v>16</v>
+      </c>
       <c r="F49" t="s">
         <v>15</v>
       </c>
@@ -2013,7 +2022,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2023,11 +2032,14 @@
       <c r="C50" t="s">
         <v>14</v>
       </c>
-      <c r="E50" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F50" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2037,11 +2049,11 @@
       <c r="C51" t="s">
         <v>14</v>
       </c>
-      <c r="K51" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>108</v>
       </c>
@@ -2065,28 +2077,45 @@
       <c r="C53" t="s">
         <v>14</v>
       </c>
-      <c r="D53" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="K53" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s">
         <v>18</v>
       </c>
-      <c r="H53" t="s">
-        <v>15</v>
-      </c>
-      <c r="I53" t="s">
-        <v>15</v>
-      </c>
-      <c r="J53" t="s">
-        <v>15</v>
-      </c>
-      <c r="K53" t="s">
-        <v>15</v>
-      </c>
-      <c r="L53" t="s">
+      <c r="H54" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" t="s">
+        <v>15</v>
+      </c>
+      <c r="L54" t="s">
         <v>15</v>
       </c>
     </row>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A1ADEA-25DE-4251-A0C5-6A654028371B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B57551-B04D-4D00-81AB-9309722A7ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 22-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 07-10-2026'!$A$1:$L$54</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="112">
   <si>
     <t>Standard</t>
   </si>
@@ -55,13 +55,13 @@
     <t>WinPLC _Privath__ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _Privath__ (XMedicus Systems)</t>
+    <t>XMedicus _Privath__ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _Privath__ (CGM)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0130X)</t>
@@ -104,6 +104,12 @@
   </si>
   <si>
     <t>DDB (1.1)</t>
+  </si>
+  <si>
+    <t>Den Gode Blanketservice</t>
+  </si>
+  <si>
+    <t>DGB (0.91)</t>
   </si>
   <si>
     <t>Udskrivningsepikrise</t>
@@ -694,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -926,6 +932,9 @@
       <c r="C7" t="s">
         <v>14</v>
       </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
       <c r="K7" t="s">
         <v>15</v>
       </c>
@@ -940,34 +949,16 @@
       <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" t="s">
-        <v>15</v>
+      <c r="E8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -975,14 +966,11 @@
       <c r="D9" t="s">
         <v>15</v>
       </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
       <c r="F9" t="s">
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -992,9 +980,6 @@
       </c>
       <c r="J9" t="s">
         <v>15</v>
-      </c>
-      <c r="K9" t="s">
-        <v>18</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -1002,7 +987,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1013,11 +998,14 @@
       <c r="D10" t="s">
         <v>15</v>
       </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
       <c r="F10" t="s">
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -1027,6 +1015,9 @@
       </c>
       <c r="J10" t="s">
         <v>15</v>
+      </c>
+      <c r="K10" t="s">
+        <v>18</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -1034,10 +1025,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -1045,14 +1036,11 @@
       <c r="D11" t="s">
         <v>15</v>
       </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
       <c r="F11" t="s">
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -1062,9 +1050,6 @@
       </c>
       <c r="J11" t="s">
         <v>15</v>
-      </c>
-      <c r="K11" t="s">
-        <v>16</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
@@ -1072,7 +1057,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -1083,8 +1068,14 @@
       <c r="D12" t="s">
         <v>15</v>
       </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -1094,6 +1085,9 @@
       </c>
       <c r="J12" t="s">
         <v>15</v>
+      </c>
+      <c r="K12" t="s">
+        <v>16</v>
       </c>
       <c r="L12" t="s">
         <v>15</v>
@@ -1101,10 +1095,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -1112,11 +1106,8 @@
       <c r="D13" t="s">
         <v>15</v>
       </c>
-      <c r="E13" t="s">
-        <v>16</v>
-      </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -1126,9 +1117,6 @@
       </c>
       <c r="J13" t="s">
         <v>15</v>
-      </c>
-      <c r="K13" t="s">
-        <v>16</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1136,7 +1124,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
@@ -1150,11 +1138,8 @@
       <c r="E14" t="s">
         <v>16</v>
       </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -1166,7 +1151,7 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
@@ -1185,6 +1170,12 @@
       <c r="D15" t="s">
         <v>15</v>
       </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
@@ -1198,7 +1189,7 @@
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L15" t="s">
         <v>15</v>
@@ -1217,9 +1208,6 @@
       <c r="D16" t="s">
         <v>15</v>
       </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
       <c r="G16" t="s">
         <v>15</v>
       </c>
@@ -1241,10 +1229,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -1256,7 +1244,7 @@
         <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -1276,7 +1264,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
         <v>44</v>
@@ -1288,10 +1276,10 @@
         <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -1322,9 +1310,6 @@
       <c r="D19" t="s">
         <v>15</v>
       </c>
-      <c r="E19" t="s">
-        <v>16</v>
-      </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
@@ -1360,11 +1345,14 @@
       <c r="D20" t="s">
         <v>15</v>
       </c>
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -1392,8 +1380,29 @@
       <c r="C21" t="s">
         <v>14</v>
       </c>
-      <c r="E21" t="s">
-        <v>16</v>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1406,32 +1415,8 @@
       <c r="C22" t="s">
         <v>14</v>
       </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
       <c r="E22" t="s">
         <v>16</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1447,6 +1432,9 @@
       <c r="D23" t="s">
         <v>15</v>
       </c>
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
       <c r="F23" t="s">
         <v>15</v>
       </c>
@@ -1479,8 +1467,29 @@
       <c r="C24" t="s">
         <v>14</v>
       </c>
-      <c r="E24" t="s">
-        <v>16</v>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1493,34 +1502,16 @@
       <c r="C25" t="s">
         <v>14</v>
       </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25" t="s">
-        <v>15</v>
+      <c r="E25" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -1529,10 +1520,10 @@
         <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -1541,9 +1532,6 @@
         <v>15</v>
       </c>
       <c r="J26" t="s">
-        <v>15</v>
-      </c>
-      <c r="K26" t="s">
         <v>15</v>
       </c>
       <c r="L26" t="s">
@@ -1552,7 +1540,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
         <v>61</v>
@@ -1563,11 +1551,14 @@
       <c r="D27" t="s">
         <v>15</v>
       </c>
+      <c r="E27" t="s">
+        <v>16</v>
+      </c>
       <c r="F27" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -1576,6 +1567,9 @@
         <v>15</v>
       </c>
       <c r="J27" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" t="s">
         <v>15</v>
       </c>
       <c r="L27" t="s">
@@ -1584,10 +1578,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -1596,10 +1590,10 @@
         <v>15</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -1609,9 +1603,6 @@
       </c>
       <c r="J28" t="s">
         <v>15</v>
-      </c>
-      <c r="K28" t="s">
-        <v>16</v>
       </c>
       <c r="L28" t="s">
         <v>15</v>
@@ -1619,7 +1610,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
         <v>64</v>
@@ -1631,10 +1622,10 @@
         <v>15</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -1644,6 +1635,9 @@
       </c>
       <c r="J29" t="s">
         <v>15</v>
+      </c>
+      <c r="K29" t="s">
+        <v>16</v>
       </c>
       <c r="L29" t="s">
         <v>15</v>
@@ -1651,10 +1645,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -1663,10 +1657,10 @@
         <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -1675,9 +1669,6 @@
         <v>15</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
-      </c>
-      <c r="K30" t="s">
         <v>15</v>
       </c>
       <c r="L30" t="s">
@@ -1686,7 +1677,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
         <v>67</v>
@@ -1698,10 +1689,10 @@
         <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -1710,6 +1701,9 @@
         <v>15</v>
       </c>
       <c r="J31" t="s">
+        <v>15</v>
+      </c>
+      <c r="K31" t="s">
         <v>15</v>
       </c>
       <c r="L31" t="s">
@@ -1718,42 +1712,39 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>68</v>
-      </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
-      <c r="K32" t="s">
-        <v>15</v>
-      </c>
-      <c r="L32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>69</v>
       </c>
       <c r="B33" t="s">
         <v>70</v>
@@ -1761,11 +1752,32 @@
       <c r="C33" t="s">
         <v>14</v>
       </c>
-      <c r="E33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" t="s">
+        <v>15</v>
+      </c>
+      <c r="K33" t="s">
+        <v>15</v>
+      </c>
+      <c r="L33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1834,11 +1846,8 @@
       <c r="E38" t="s">
         <v>16</v>
       </c>
-      <c r="K38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1885,8 +1894,11 @@
       <c r="E41" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1896,11 +1908,11 @@
       <c r="C42" t="s">
         <v>14</v>
       </c>
-      <c r="K42" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,23 +1926,23 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>91</v>
-      </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="K44" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>92</v>
       </c>
       <c r="B45" t="s">
         <v>93</v>
@@ -1938,14 +1950,11 @@
       <c r="C45" t="s">
         <v>14</v>
       </c>
-      <c r="F45" t="s">
-        <v>15</v>
-      </c>
       <c r="K45" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1955,14 +1964,14 @@
       <c r="C46" t="s">
         <v>14</v>
       </c>
-      <c r="E46" t="s">
-        <v>16</v>
-      </c>
       <c r="F46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1975,8 +1984,11 @@
       <c r="E47" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1988,12 +2000,6 @@
       </c>
       <c r="E48" t="s">
         <v>16</v>
-      </c>
-      <c r="F48" t="s">
-        <v>15</v>
-      </c>
-      <c r="K48" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2006,6 +2012,9 @@
       <c r="C49" t="s">
         <v>14</v>
       </c>
+      <c r="E49" t="s">
+        <v>16</v>
+      </c>
       <c r="F49" t="s">
         <v>15</v>
       </c>
@@ -2023,8 +2032,11 @@
       <c r="C50" t="s">
         <v>14</v>
       </c>
-      <c r="E50" t="s">
-        <v>16</v>
+      <c r="F50" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2037,8 +2049,8 @@
       <c r="C51" t="s">
         <v>14</v>
       </c>
-      <c r="K51" t="s">
-        <v>15</v>
+      <c r="E51" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2065,28 +2077,45 @@
       <c r="C53" t="s">
         <v>14</v>
       </c>
-      <c r="D53" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="K53" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s">
         <v>18</v>
       </c>
-      <c r="H53" t="s">
-        <v>15</v>
-      </c>
-      <c r="I53" t="s">
-        <v>15</v>
-      </c>
-      <c r="J53" t="s">
-        <v>15</v>
-      </c>
-      <c r="K53" t="s">
-        <v>15</v>
-      </c>
-      <c r="L53" t="s">
+      <c r="H54" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" t="s">
+        <v>15</v>
+      </c>
+      <c r="L54" t="s">
         <v>15</v>
       </c>
     </row>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9B0D537D149892B7B36B38FCE70D85E9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E0013FA-7CB5-432C-BC83-206EAAE9DF0D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA69FB9-66B5-4552-8B57-8548C1F23318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 02-10-2026'!$A$1:$L$54</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 07-10-2026'!$A$1:$L$54</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -701,9 +701,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -741,7 +741,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -773,7 +773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -808,7 +808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -846,7 +846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -884,7 +884,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -922,7 +922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -939,7 +939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -953,7 +953,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -985,7 +985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>65</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>65</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>91</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>108</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>110</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA69FB9-66B5-4552-8B57-8548C1F23318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9B0553DE3E16B227B36B38FCE70D85E9B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D39823C7-5C87-4BD1-98E6-881E484C5930}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 07-10-2026'!$A$1:$L$54</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 08-10-2026'!$A$1:$L$54</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9B0553DE3E16B227B36B38FCE70D85E9B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D39823C7-5C87-4BD1-98E6-881E484C5930}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6D9AAA-3CC1-4288-81F8-802E404252EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 08-10-2026'!$A$1:$L$54</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 09-10-2026'!$A$1:$L$54</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6D9AAA-3CC1-4288-81F8-802E404252EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110263E3-E853-4C6A-9A47-66D6D8AF5C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110263E3-E853-4C6A-9A47-66D6D8AF5C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9842DF68D0F693EF82EB2A8E071D859EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CB9FE1B-D14B-4A9C-9F12-1782364EB3CE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 09-10-2026'!$A$1:$L$54</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 23-10-2026'!$A$1:$M$55</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="115">
   <si>
     <t>Standard</t>
   </si>
@@ -52,6 +52,9 @@
     <t>NOVAX _Privath__ (Novax)</t>
   </si>
   <si>
+    <t>Potensklinikken CRM (Potensklinikken)</t>
+  </si>
+  <si>
     <t>WinPLC _Privath__ (EG)</t>
   </si>
   <si>
@@ -341,6 +344,12 @@
   </si>
   <si>
     <t>XREF06 (XH0631R)</t>
+  </si>
+  <si>
+    <t>LaboratoryReport</t>
+  </si>
+  <si>
+    <t>XRPT01 (XR0130K)</t>
   </si>
   <si>
     <t>CervixcytologyReport</t>
@@ -700,10 +709,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -740,1383 +749,1427 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>18</v>
-      </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="M10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K12" t="s">
         <v>16</v>
       </c>
       <c r="L12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="M12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14" t="s">
         <v>16</v>
       </c>
       <c r="L14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="M14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" t="s">
         <v>16</v>
       </c>
       <c r="L16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="M16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>43</v>
       </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" t="s">
-        <v>15</v>
-      </c>
-      <c r="K17" t="s">
-        <v>16</v>
-      </c>
-      <c r="L17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>42</v>
-      </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>60</v>
       </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" t="s">
-        <v>15</v>
-      </c>
-      <c r="L26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>59</v>
-      </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>63</v>
       </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" t="s">
-        <v>15</v>
-      </c>
-      <c r="L28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>62</v>
-      </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K29" t="s">
         <v>16</v>
       </c>
       <c r="L29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="M29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>66</v>
       </c>
-      <c r="C30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" t="s">
-        <v>15</v>
-      </c>
-      <c r="L30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>65</v>
-      </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>69</v>
       </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
-      <c r="L32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>68</v>
-      </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I33" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>16</v>
-      </c>
-      <c r="K39" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>16</v>
-      </c>
-      <c r="K40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>16</v>
-      </c>
-      <c r="K41" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="L43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="L44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>92</v>
       </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="K44" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>91</v>
-      </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
-      </c>
-      <c r="K45" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="L45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>15</v>
-      </c>
-      <c r="K46" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="L46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F49" t="s">
-        <v>15</v>
-      </c>
-      <c r="K49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="L49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F50" t="s">
-        <v>15</v>
-      </c>
-      <c r="K50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="L50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
-      </c>
-      <c r="K52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C53" t="s">
-        <v>14</v>
-      </c>
-      <c r="K53" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="L53" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" t="s">
-        <v>15</v>
-      </c>
-      <c r="E54" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" t="s">
-        <v>15</v>
-      </c>
-      <c r="G54" t="s">
-        <v>18</v>
-      </c>
-      <c r="H54" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" t="s">
-        <v>15</v>
-      </c>
-      <c r="J54" t="s">
-        <v>15</v>
-      </c>
-      <c r="K54" t="s">
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" t="s">
+        <v>16</v>
+      </c>
+      <c r="K55" t="s">
+        <v>16</v>
+      </c>
+      <c r="L55" t="s">
+        <v>16</v>
+      </c>
+      <c r="M55" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
